--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/PENNSYLVANIA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/PENNSYLVANIA_2015.xlsx
@@ -2749,7 +2749,7 @@
         <v>62</v>
       </c>
       <c r="D133">
-        <v>0.009503372164316371</v>
+        <v>0.009503372164316373</v>
       </c>
     </row>
     <row r="134">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C196">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C546">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C571">
@@ -13891,7 +13891,7 @@
         <v>62</v>
       </c>
       <c r="D752">
-        <v>0.009503372164316371</v>
+        <v>0.009503372164316373</v>
       </c>
     </row>
     <row r="753">
